--- a/stories/arbres/ATOM-VIV.ANI.003-04.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.003-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Grégoire est dans le jardin avec maman. Le lapin gris remue le nez. Sa gamelle d'eau est vide. Grégoire veut aider. Maman dit : on le fait ensemble. On est doux. On le fait avec un adulte. Maman verse l'eau. Grégoire tient le bol avec maman. L'eau arrive tout doucement. Ça fait un petit bruit. Maman met une feuille de salade. Grégoire pose la gamelle. Il est doux. Sa main va lentement. Le lapin vient. Il boit. Il croque. Maman dit : on prend soin avec un adulte. On reste doux. Grégoire recule un peu. Il reste calme. Le lapin mange encore. L'herbe sent le matin.</t>
+          <t>Grégoire est dans le jardin avec maman. Le lapin gris remue le nez. Sa gamelle d'eau est vide. Grégoire veut aider. On le fait ensemble. On est doux. On le fait avec un adulte. Maman verse l'eau. Grégoire tient le bol avec maman. L'eau arrive tout doucement. Ça fait un petit bruit. Maman met une feuille de salade. Grégoire pose la gamelle. Il est doux. Sa main va lentement. Le lapin vient. Il boit. Il croque. On prend soin avec un adulte. On reste doux. Grégoire recule un peu. Il reste calme. Le lapin mange encore. L'herbe sent le matin.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Grégoire est dans le jardin avec maman. Le lapin gris remue le nez. Sa gamelle d'eau est vide. Grégoire veut aider.
+maman|On le fait ensemble. On est doux. On le fait avec un adulte. Maman verse l'eau.
+narrateur|Grégoire tient le bol avec maman. L'eau arrive tout doucement. Ça fait un petit bruit. Maman met une feuille de salade. Grégoire pose la gamelle. Il est doux. Sa main va lentement. Le lapin vient. Il boit. Il croque.
+maman|On prend soin avec un adulte. On reste doux.
+narrateur|Grégoire recule un peu. Il reste calme. Le lapin mange encore. L'herbe sent le matin.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Grégoire donne l'eau au lapin. Comment fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Grégoire a été doux. Il a versé l'eau avec un adulte. Maman était là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1826,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Le lapin remue encore le nez. Grégoire s'assoit près de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1993,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2033,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.003-04.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.003-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Grégoire recule un peu. Il reste calme. Le lapin mange encore. L'herbe sent le matin.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|Grégoire donne l'eau au lapin. Comment fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1675,7 @@
           <t>narrateur|Grégoire a été doux. Il a versé l'eau avec un adulte. Maman était là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1831,6 +1839,7 @@
           <t>narrateur|Le lapin remue encore le nez. Grégoire s'assoit près de maman.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1998,6 +2007,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2016,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2040,6 +2050,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2241,6 +2265,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-VIV.ANI.003-04.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.003-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Grégoire donne l'eau au lapin</t>
+          <t>La bouteille coincée</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nina veut que le lapin boive. La bouteille à l'envers est coincée. Maman aide. Le lapin boit.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Grégoire est dans le jardin avec maman. Le lapin gris remue le nez. Sa gamelle d'eau est vide. Grégoire veut aider. On le fait ensemble. On est doux. On le fait avec un adulte. Maman verse l'eau. Grégoire tient le bol avec maman. L'eau arrive tout doucement. Ça fait un petit bruit. Maman met une feuille de salade. Grégoire pose la gamelle. Il est doux. Sa main va lentement. Le lapin vient. Il boit. Il croque. On prend soin avec un adulte. On reste doux. Grégoire recule un peu. Il reste calme. Le lapin mange encore. L'herbe sent le matin.</t>
+          <t>Les fanes de carotte sentent la terre. Elles sont encore un peu humides. Sur la table du jardin, un couteau de bois attend. On garde les fanes, Nina. Pour le lapin. Il a faim ? Il a soif aussi. Je veux qu'il boive. On y va ensemble. Le figuier fait une ombre ronde. Des feuilles tapent, tout doux. En ce moment, Nina est devant le clapier. Le lapin gris remue le nez. Sa bouteille d'eau est à l'envers. Le goulot devrait donner une goutte. Rien ne tombe. Il n'a plus d'eau. Regarde. Elle est coincée. La bouteille a tourné de travers. Le fil de fer la pince trop fort. Je tire ? On le fait avec un adulte. On est doux. Tu tiens le bol, moi le fil ? Oui, maman. Nina tient le petit bol. Maman desserre le fil, tout lentement. La bouteille se redresse. Une goutte apparaît. Puis une autre. Ça marche. On remplit aussi le bol ? Un peu. Elles versent l'eau ensemble. Le bol se pose près de la grille, tout doux. Nina recule d'un pas. On reste près de moi. Le lapin s'approche. Son nez touche la goutte de la bouteille. Il boit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Grégoire est dans le jardin &lt;emphasis level="moderate"&gt;avec&lt;/emphasis&gt; maman. Le lapin gris remue le nez. Sa gamelle d'eau est vide. Grégoire veut aider. Maman dit : on le fait ensemble. On est doux. On le fait avec un adulte. Maman verse l'eau. Grégoire tient le bol avec maman. L'eau arrive tout doucement. Ça fait un petit bruit. Maman met une feuille de salade. Grégoire pose la gamelle. Il est doux. Sa main va lentement. Le lapin vient. Il boit. Il croque. Maman dit : on prend soin avec un adulte. On reste doux. Grégoire recule un peu. Il reste calme. Le lapin mange encore. L'herbe sent le matin.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les fanes de carotte sentent la terre. Elles sont encore un peu humides. Sur la table du jardin, un couteau de bois attend. On garde les fanes, Nina. Pour le lapin. Il a faim ? Il a soif aussi. Je veux qu'il boive. On y va ensemble. Le figuier fait une ombre ronde. Des feuilles tapent, tout doux. En ce moment, Nina est devant le clapier. Le lapin gris remue le nez. Sa bouteille d'eau est à l'envers. Le goulot devrait donner une goutte. Rien ne tombe. Il n'a plus d'eau. Regarde. Elle est coincée. La bouteille a tourné de travers. Le fil de fer la pince trop fort. Je tire ? On le fait avec un adulte. On est doux. Tu tiens le bol, moi le fil ? Oui, maman. Nina tient le petit bol. Maman desserre le fil, tout lentement. La bouteille se redresse. Une goutte apparaît. Puis une autre. Ça marche. On remplit aussi le bol ? Un peu. Elles versent l'eau ensemble. Le bol se pose près de la grille, tout doux. Nina recule d'un pas. On reste près de moi. Le lapin s'approche. Son nez touche la goutte de la bouteille. Il boit.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,14 +1324,49 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Grégoire est dans le jardin avec maman. Le lapin gris remue le nez. Sa gamelle d'eau est vide. Grégoire veut aider.
-maman|On le fait ensemble. On est doux. On le fait avec un adulte. Maman verse l'eau.
-narrateur|Grégoire tient le bol avec maman. L'eau arrive tout doucement. Ça fait un petit bruit. Maman met une feuille de salade. Grégoire pose la gamelle. Il est doux. Sa main va lentement. Le lapin vient. Il boit. Il croque.
-maman|On prend soin avec un adulte. On reste doux.
-narrateur|Grégoire recule un peu. Il reste calme. Le lapin mange encore. L'herbe sent le matin.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Les fanes de carotte sentent la terre.
+narrateur|Elles sont encore un peu humides.
+narrateur|Sur la table du jardin, un couteau de bois attend.
+maman|On garde les fanes, Nina.
+maman|Pour le lapin.
+enfant-f|Il a faim ?
+enfant-f|Il a soif aussi.
+enfant-f|Je veux qu'il boive.
+maman|On y va ensemble.
+narrateur|Le figuier fait une ombre ronde.
+narrateur|Des feuilles tapent, tout doux.
+narrateur|En ce moment, Nina est devant le clapier.
+narrateur|Le lapin gris remue le nez.
+narrateur|Sa bouteille d'eau est à l'envers.
+narrateur|Le goulot devrait donner une goutte.
+narrateur|Rien ne tombe.
+enfant-f|Il n'a plus d'eau.
+maman|Regarde.
+maman|Elle est coincée.
+narrateur|La bouteille a tourné de travers.
+narrateur|Le fil de fer la pince trop fort.
+enfant-f|Je tire ?
+maman|On le fait avec un adulte.
+maman|On est doux.
+maman|Tu tiens le bol, moi le fil ?
+enfant-f|Oui, maman.
+narrateur|Nina tient le petit bol.
+narrateur|Maman desserre le fil, tout lentement.
+narrateur|La bouteille se redresse.
+narrateur|Une goutte apparaît.
+narrateur|Puis une autre.
+enfant-f|Ça marche.
+maman|On remplit aussi le bol ?
+enfant-f|Un peu.
+narrateur|Elles versent l'eau ensemble.
+narrateur|Le bol se pose près de la grille, tout doux.
+narrateur|Nina recule d'un pas.
+maman|On reste près de moi.
+narrateur|Le lapin s'approche.
+narrateur|Son nez touche la goutte de la bouteille.
+enfant-f|Il boit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,12 +1391,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Grégoire donne l'eau au lapin. Comment fait-il ?</t>
+          <t>Nina donne l'eau au lapin. Comment fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Grégoire donne l'eau au lapin. Comment fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina donne l'eau au lapin. Comment fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1359,12 +1406,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>doux</t>
+          <t>douce</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>doux | tout doux | avec maman | avec un adulte</t>
+          <t>douce | doux | avec maman | avec un adulte</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1379,7 +1426,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il est doux, avec maman. Comment fait Grégoire ?</t>
+          <t>Elle est douce, avec maman. Comment fait Nina ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1428,7 +1475,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1500,10 +1547,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Grégoire donne l'eau au lapin. Comment fait-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Nina donne l'eau au lapin.
+narrateur|Comment fait-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1528,12 +1575,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Grégoire a été doux. Il a versé l'eau avec un adulte. Maman était là.</t>
+          <t>Le lapin lape le bol aussi. Ses moustaches bougent, très vite. Il avait vraiment soif. Oui. Tu as été douce. Avec un adulte. Merci, Nina. Tu as vu le fil ? Il pinçait. On a desserré ensemble. Nina pose une fane près de la grille. Sa main va lentement. Elle ne prend pas le lapin. Le lapin croque, puis boit encore. Carotte, et eau. Les deux. Une goutte tombe du goulot. Elle brille, puis elle part. Encore une. La bouteille n'est plus coincée.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Grégoire a été doux. Il a versé l'eau &lt;emphasis level="moderate"&gt;avec&lt;/emphasis&gt; un adulte. Maman était là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le lapin lape le bol aussi. Ses moustaches bougent, très vite. Il avait vraiment soif. Oui. Tu as été douce. Avec un adulte. Merci, Nina. Tu as vu le fil ? Il pinçait. On a desserré ensemble. Nina pose une fane près de la grille. Sa main va lentement. Elle ne prend pas le lapin. Le lapin croque, puis boit encore. Carotte, et eau. Les deux. Une goutte tombe du goulot. Elle brille, puis elle part. Encore une. La bouteille n'est plus coincée.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1596,7 +1643,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1672,10 +1719,28 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Grégoire a été doux. Il a versé l'eau avec un adulte. Maman était là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Le lapin lape le bol aussi.
+narrateur|Ses moustaches bougent, très vite.
+enfant-f|Il avait vraiment soif.
+maman|Oui.
+maman|Tu as été douce.
+maman|Avec un adulte.
+maman|Merci, Nina.
+maman|Tu as vu le fil ?
+enfant-f|Il pinçait.
+maman|On a desserré ensemble.
+narrateur|Nina pose une fane près de la grille.
+narrateur|Sa main va lentement.
+narrateur|Elle ne prend pas le lapin.
+narrateur|Le lapin croque, puis boit encore.
+enfant-f|Carotte, et eau.
+maman|Les deux.
+narrateur|Une goutte tombe du goulot.
+narrateur|Elle brille, puis elle part.
+enfant-f|Encore une.
+maman|La bouteille n'est plus coincée.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1700,12 +1765,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Le lapin remue encore le nez. Grégoire s'assoit près de maman.</t>
+          <t>Le figuier laisse passer un carré de soleil. Il tombe sur le dos du lapin. Le poil gris devient presque or. Il brille. Il a bu. C'était ça, ton envie. Nina s'assoit sur le petit banc. Maman s'assoit près d'elle. Le clapier sent le foin propre. On range les fanes ? Dans le saladier, oui. Il en reste deux, pour plus tard. Le lapin remue encore le nez. Merci, maman. On l'a fait ensemble.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le lapin remue encore le nez. Grégoire s'assoit près de maman.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le figuier laisse passer un carré de soleil. Il tombe sur le dos du lapin. Le poil gris devient presque or. Il brille. Il a bu. C'était ça, ton envie. Nina s'assoit sur le petit banc. Maman s'assoit près d'elle. Le clapier sent le foin propre. On range les fanes ? Dans le saladier, oui. Il en reste deux, pour plus tard. Le lapin remue encore le nez. Merci, maman. On l'a fait ensemble.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1768,7 +1833,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1836,10 +1901,23 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Le lapin remue encore le nez. Grégoire s'assoit près de maman.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Le figuier laisse passer un carré de soleil.
+narrateur|Il tombe sur le dos du lapin.
+narrateur|Le poil gris devient presque or.
+enfant-f|Il brille.
+maman|Il a bu.
+maman|C'était ça, ton envie.
+narrateur|Nina s'assoit sur le petit banc.
+narrateur|Maman s'assoit près d'elle.
+narrateur|Le clapier sent le foin propre.
+maman|On range les fanes ?
+enfant-f|Dans le saladier, oui.
+narrateur|Il en reste deux, pour plus tard.
+narrateur|Le lapin remue encore le nez.
+enfant-f|Merci, maman.
+maman|On l'a fait ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1864,12 +1942,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le lapin a de l'eau. La bouteille donne encore des gouttes. Une feuille de figuier tapote le bois. Le jardin sent la terre et la carotte.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le lapin a de l'eau. La bouteille donne encore des gouttes. Une feuille de figuier tapote le bois. Le jardin sent la terre et la carotte.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1925,14 +2003,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2004,10 +2082,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-f|Le lapin a de l'eau.
+maman|La bouteille donne encore des gouttes.
+narrateur|Une feuille de figuier tapote le bois.
+narrateur|Le jardin sent la terre et la carotte.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2026,7 +2106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2064,6 +2144,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.003-04.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.003-04.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin</t>
+          <t>jardin, clapier à l'ombre du figuier</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Grégoire, maman</t>
+          <t>Nina, maman</t>
         </is>
       </c>
     </row>
